--- a/pricing/商务成品/对外/定制报价/Trinity模型报价表_海外三家定制.xlsx
+++ b/pricing/商务成品/对外/定制报价/Trinity模型报价表_海外三家定制.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅有折扣" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +46,24 @@
       <name val="Menlo"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="00713F12"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="001D2939"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -77,8 +94,14 @@
         <bgColor rgb="FFE8F8F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+        <bgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -133,12 +156,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyFill="1" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyFill="1" applyFont="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -537,7 +586,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>本页为累积更新日志（新→旧），供 Trinity 对内核对；外发客户前可删本页。文件：Trinity模型报价表_海外三家定制.xlsx。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>更新说明</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026.9.20</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>海外三家</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>新增 2 款：gemini-3.8-flash、gpt-6-astra</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>定制表重建入表</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -552,1182 +675,1252 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Trinity · 折扣报价表</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>模态</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>厂商</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>模型 ID</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>刊例价·输入</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>刊例价·输出</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>刊例价·缓存</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>折扣</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>线路</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>生文</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>gpt-5</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>GPT-5</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Azure</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>gpt-5-nano</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>GPT-5 Nano</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
+      <c r="I4" s="10" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>gpt-5.1</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>GPT-5.1</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n"/>
+      <c r="I5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>gpt-5.2</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>GPT-5.2</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>14.00</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n"/>
+      <c r="I6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>gpt-5.3-codex</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>GPT-5.3 Codex</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>14.00</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>GPT-5.4</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>gpt-5.4-mini</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>GPT-5.4 Mini</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>gpt-5.4-nano</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>GPT-5.4 nano</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>gpt-5.4-pro</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>GPT-5.4 Pro</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>180.00</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>gpt-5.5</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>gpt-5.6-sol</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>gpt-5.6-terra</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>GPT-5.6 Terra</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>5.5折</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n"/>
+      <c r="I15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>gpt-6-astra</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>GPT-6 Astra</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>8.5折</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>claude-fable-5</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Claude Fable 5</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>8.3折</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Claude Opus 4.6</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>8.3折</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="I18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>claude-opus-4-7</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Claude Opus 4.7</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>8.3折</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="I19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>claude-opus-4-8</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Claude Opus 4.8</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>8.3折</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>claude-opus-5</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>8.3折</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="I21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Claude Sonnet 4.6</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>8.3折</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="I22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Claude Sonnet 5</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>8.3折</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="I23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>gemini-2.5-flash</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Gemini 2.5 Flash</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I24" s="15" t="inlineStr">
         <is>
           <t>Google Cloud</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="12" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-lite</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Gemini 2.5 Flash Lite</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="I25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>gemini-2.5-pro</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Gemini 2.5 Pro</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G26" s="17" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="I26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>gemini-3-flash-preview</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Gemini 3 Flash Preview</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="I27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>gemini-3.1-flash-lite</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Gemini 3.1 Flash Lite</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="I28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Gemini 3.1 Pro Preview</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="I29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>gemini-3.1-pro-preview-customtools</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Gemini 3.1 Pro Preview Custom Tools</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="I30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>gemini-3.5-flash</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Gemini 3.5 Flash</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>9.00</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="I31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>gemini-3.5-flash-lite</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Gemini 3.5 Flash Lite</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>8.2折</t>
         </is>
       </c>
-      <c r="I31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="I32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>gemini-3.6-flash</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>Gemini 3.6 Flash</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="I33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>gemini-3.7-flash</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Gemini 3.7 Flash</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>7.5折</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n"/>
+      <c r="I34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>gemini-3.8-flash</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Gemini 3.8 Flash</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t>8.2折</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="I23:I33"/>
-    <mergeCell ref="I3:I15"/>
+    <mergeCell ref="I24:I35"/>
+    <mergeCell ref="I3:I16"/>
+    <mergeCell ref="B17:B23"/>
+    <mergeCell ref="B3:B16"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:A33"/>
-    <mergeCell ref="I16:I22"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="B16:B22"/>
-    <mergeCell ref="B23:B33"/>
+    <mergeCell ref="B24:B35"/>
+    <mergeCell ref="I17:I23"/>
+    <mergeCell ref="A3:A35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
